--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91899</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91899</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91551</v>
+        <v>91557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100124</v>
+        <v>100130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100124</v>
+        <v>100130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100124</v>
+        <v>100130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100124</v>
+        <v>100130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100124</v>
+        <v>100130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91905</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91905</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100130</v>
+        <v>100134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100130</v>
+        <v>100134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100130</v>
+        <v>100134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100130</v>
+        <v>100134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100130</v>
+        <v>100134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100134</v>
+        <v>100136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100134</v>
+        <v>100136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100134</v>
+        <v>100136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100134</v>
+        <v>100136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100134</v>
+        <v>100136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>91911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100136</v>
+        <v>100138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100136</v>
+        <v>100138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100136</v>
+        <v>100138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100136</v>
+        <v>100138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100136</v>
+        <v>100138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91911</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91911</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100138</v>
+        <v>100151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100138</v>
+        <v>100151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100138</v>
+        <v>100151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100138</v>
+        <v>100151</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100138</v>
+        <v>100151</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100151</v>
+        <v>100153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100151</v>
+        <v>100153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100151</v>
+        <v>100153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100151</v>
+        <v>100153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100151</v>
+        <v>100153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91926</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91926</v>
+        <v>91929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100153</v>
+        <v>100156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100153</v>
+        <v>100156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100153</v>
+        <v>100156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100153</v>
+        <v>100156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100153</v>
+        <v>100156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91929</v>
+        <v>91939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91929</v>
+        <v>91939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100156</v>
+        <v>100166</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100156</v>
+        <v>100166</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100156</v>
+        <v>100166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100156</v>
+        <v>100166</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100156</v>
+        <v>100166</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100166</v>
+        <v>100167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100166</v>
+        <v>100167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100166</v>
+        <v>100167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100166</v>
+        <v>100167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100166</v>
+        <v>100167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100167</v>
+        <v>100172</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100167</v>
+        <v>100172</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100167</v>
+        <v>100172</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100167</v>
+        <v>100172</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100167</v>
+        <v>100172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100172</v>
+        <v>100175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100172</v>
+        <v>100175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100172</v>
+        <v>100175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100172</v>
+        <v>100175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100172</v>
+        <v>100175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100175</v>
+        <v>100181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100175</v>
+        <v>100181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100175</v>
+        <v>100181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100175</v>
+        <v>100181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100175</v>
+        <v>100181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100181</v>
+        <v>100193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100181</v>
+        <v>100193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100181</v>
+        <v>100193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100181</v>
+        <v>100193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100181</v>
+        <v>100193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100193</v>
+        <v>100194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100193</v>
+        <v>100194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100193</v>
+        <v>100194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100193</v>
+        <v>100194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100193</v>
+        <v>100194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100194</v>
+        <v>100197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100194</v>
+        <v>100197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100194</v>
+        <v>100197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>100197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100194</v>
+        <v>100197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 9543-2026 artfynd.xlsx
+++ b/artfynd/A 9543-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137105315</v>
       </c>
       <c r="B2" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137105317</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137105319</v>
       </c>
       <c r="B4" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137105321</v>
       </c>
       <c r="B5" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137105329</v>
       </c>
       <c r="B6" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137106639</v>
       </c>
       <c r="B7" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137106642</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137105332</v>
       </c>
       <c r="B9" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137105322</v>
       </c>
       <c r="B10" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137105335</v>
       </c>
       <c r="B11" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137106641</v>
       </c>
       <c r="B12" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137105318</v>
       </c>
       <c r="B13" t="n">
-        <v>110430</v>
+        <v>110436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137105323</v>
       </c>
       <c r="B14" t="n">
-        <v>100197</v>
+        <v>100201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137105325</v>
       </c>
       <c r="B15" t="n">
-        <v>100197</v>
+        <v>100201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137105326</v>
       </c>
       <c r="B16" t="n">
-        <v>100197</v>
+        <v>100201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137105334</v>
       </c>
       <c r="B17" t="n">
-        <v>100197</v>
+        <v>100201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137105336</v>
       </c>
       <c r="B18" t="n">
-        <v>100197</v>
+        <v>100201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137105320</v>
       </c>
       <c r="B19" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>137105324</v>
       </c>
       <c r="B20" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137105328</v>
       </c>
       <c r="B21" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137105330</v>
       </c>
       <c r="B22" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>137105331</v>
       </c>
       <c r="B23" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137106640</v>
       </c>
       <c r="B24" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>137106643</v>
       </c>
       <c r="B25" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
